--- a/TP4/coeficientes_logit_comparacion_2025.xlsx
+++ b/TP4/coeficientes_logit_comparacion_2025.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,45 +457,349 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.8383028933666246</v>
+        <v>-2.127173533657947</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>-2.492832494901692</v>
       </c>
       <c r="D2" t="n">
-        <v>1.824292084474262e-06</v>
+        <v>-1.372619831395561</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>edad</t>
+          <t>Distincion_vivienda_hogar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.01654030052754243</v>
+        <v>-0.4324600236653054</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0.133952137512471</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0111373558905682</v>
+        <v>-0.400889981800908</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>genero</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.3018868326318967</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.3874964280888701</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.09509353414700764</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>edad</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.08622628393497969</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.07439189915012812</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.08480551191839436</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>tipo_empleo</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.07941006410819404</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.09556845140422197</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.08233754426461207</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>parentesco</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.09647126130217008</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.09518034792146739</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.09309889212543432</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>nivel_educ</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-0.01878786445224619</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.01086197980788514</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.0478992290188085</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>estado_empleo</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>-0.03290485192334106</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.0353814748475314</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.1775841739364851</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>categoria_inactividad</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.3483953357708522</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.3262309279823044</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.3539353471984567</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tipo_cobertura_salud</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.6809113612266906</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.585595665079245</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.445630941533774</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>obra_social</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-0.4373581067872873</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.5163134163585051</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.4308008893603412</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>nivel_ocupacion</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.2803581822670167</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.2408121754493609</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.220079893467959</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>tipo_contrato</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.4195235978774553</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.4131076170516574</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.4207613757799708</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>empleo</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.140302969760727</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.0772543781436431</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.04129235108006517</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>busqueda_empleo</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.4909757814356</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.309800500281941</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.299047306758968</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>medio_busqueda_empleo</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>-4.586808972193319</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-2.90084227045227</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-2.945823226328595</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>n_personas</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.2920734760066747</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.3494492899790355</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.1450765671581794</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>adulto_equiv</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.905157489318497</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.41177911417214</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.779312994560645</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>ad_equiv_hogar</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>0.2476893494048354</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.001039482967446708</v>
+      <c r="B20" t="n">
+        <v>-0.1885578641911002</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.2504844073827546</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.02899557941119176</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>edad2</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>-0.001122750128137846</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.0009970890600360183</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.00116655058901435</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>educ</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>-0.03248373625743606</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.04963920138151054</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.04827981137955573</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>horastrab</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>-0.01885868423953722</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.01877494542342938</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.01938721137799903</v>
       </c>
     </row>
   </sheetData>

--- a/TP4/coeficientes_logit_comparacion_2025.xlsx
+++ b/TP4/coeficientes_logit_comparacion_2025.xlsx
@@ -460,7 +460,7 @@
         <v>-2.127173533657947</v>
       </c>
       <c r="C2" t="n">
-        <v>-2.492832494901692</v>
+        <v>-2.50409612201991</v>
       </c>
       <c r="D2" t="n">
         <v>-1.372619831395561</v>
@@ -476,7 +476,7 @@
         <v>-0.4324600236653054</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.133952137512471</v>
+        <v>-0.1463397933141267</v>
       </c>
       <c r="D3" t="n">
         <v>-0.400889981800908</v>
@@ -492,7 +492,7 @@
         <v>0.3018868326318967</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3874964280888701</v>
+        <v>0.3767350305831155</v>
       </c>
       <c r="D4" t="n">
         <v>0.09509353414700764</v>
@@ -508,7 +508,7 @@
         <v>0.08622628393497969</v>
       </c>
       <c r="C5" t="n">
-        <v>0.07439189915012812</v>
+        <v>0.07207139829128287</v>
       </c>
       <c r="D5" t="n">
         <v>0.08480551191839436</v>
@@ -524,7 +524,7 @@
         <v>0.07941006410819404</v>
       </c>
       <c r="C6" t="n">
-        <v>0.09556845140422197</v>
+        <v>0.09319649743548022</v>
       </c>
       <c r="D6" t="n">
         <v>0.08233754426461207</v>
@@ -540,7 +540,7 @@
         <v>0.09647126130217008</v>
       </c>
       <c r="C7" t="n">
-        <v>0.09518034792146739</v>
+        <v>0.09554837265743082</v>
       </c>
       <c r="D7" t="n">
         <v>0.09309889212543432</v>
@@ -556,7 +556,7 @@
         <v>-0.01878786445224619</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.01086197980788514</v>
+        <v>-0.01432410974989314</v>
       </c>
       <c r="D8" t="n">
         <v>-0.0478992290188085</v>
@@ -572,7 +572,7 @@
         <v>-0.03290485192334106</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.0353814748475314</v>
+        <v>-0.05292743970908468</v>
       </c>
       <c r="D9" t="n">
         <v>-0.1775841739364851</v>
@@ -588,7 +588,7 @@
         <v>0.3483953357708522</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3262309279823044</v>
+        <v>0.3289679624640249</v>
       </c>
       <c r="D10" t="n">
         <v>0.3539353471984567</v>
@@ -604,7 +604,7 @@
         <v>-0.6809113612266906</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.585595665079245</v>
+        <v>-0.5765869686178934</v>
       </c>
       <c r="D11" t="n">
         <v>-0.445630941533774</v>
@@ -620,7 +620,7 @@
         <v>-0.4373581067872873</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.5163134163585051</v>
+        <v>-0.5158052556150698</v>
       </c>
       <c r="D12" t="n">
         <v>-0.4308008893603412</v>
@@ -636,7 +636,7 @@
         <v>-0.2803581822670167</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.2408121754493609</v>
+        <v>-0.2400501091994265</v>
       </c>
       <c r="D13" t="n">
         <v>-0.220079893467959</v>
@@ -652,7 +652,7 @@
         <v>0.4195235978774553</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4131076170516574</v>
+        <v>0.4130466624286052</v>
       </c>
       <c r="D14" t="n">
         <v>0.4207613757799708</v>
@@ -668,7 +668,7 @@
         <v>0.140302969760727</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0772543781436431</v>
+        <v>0.06649989208873208</v>
       </c>
       <c r="D15" t="n">
         <v>-0.04129235108006517</v>
@@ -684,7 +684,7 @@
         <v>1.4909757814356</v>
       </c>
       <c r="C16" t="n">
-        <v>1.309800500281941</v>
+        <v>1.309209272103024</v>
       </c>
       <c r="D16" t="n">
         <v>1.299047306758968</v>
@@ -700,7 +700,7 @@
         <v>-4.586808972193319</v>
       </c>
       <c r="C17" t="n">
-        <v>-2.90084227045227</v>
+        <v>-2.903806902757876</v>
       </c>
       <c r="D17" t="n">
         <v>-2.945823226328595</v>
@@ -716,7 +716,7 @@
         <v>0.2920734760066747</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3494492899790355</v>
+        <v>0.3418805874017823</v>
       </c>
       <c r="D18" t="n">
         <v>0.1450765671581794</v>
@@ -732,7 +732,7 @@
         <v>2.905157489318497</v>
       </c>
       <c r="C19" t="n">
-        <v>3.41177911417214</v>
+        <v>3.349315458954955</v>
       </c>
       <c r="D19" t="n">
         <v>1.779312994560645</v>
@@ -748,7 +748,7 @@
         <v>-0.1885578641911002</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.2504844073827546</v>
+        <v>-0.241833629459727</v>
       </c>
       <c r="D20" t="n">
         <v>-0.02899557941119176</v>
@@ -764,7 +764,7 @@
         <v>-0.001122750128137846</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0009970890600360183</v>
+        <v>-0.0009739479081583249</v>
       </c>
       <c r="D21" t="n">
         <v>-0.00116655058901435</v>
@@ -780,7 +780,7 @@
         <v>-0.03248373625743606</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.04963920138151054</v>
+        <v>-0.04843287787580079</v>
       </c>
       <c r="D22" t="n">
         <v>-0.04827981137955573</v>
@@ -796,7 +796,7 @@
         <v>-0.01885868423953722</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.01877494542342938</v>
+        <v>-0.0188031551219513</v>
       </c>
       <c r="D23" t="n">
         <v>-0.01938721137799903</v>

--- a/TP4/coeficientes_logit_comparacion_2025.xlsx
+++ b/TP4/coeficientes_logit_comparacion_2025.xlsx
@@ -460,7 +460,7 @@
         <v>-2.127173533657947</v>
       </c>
       <c r="C2" t="n">
-        <v>-2.50409612201991</v>
+        <v>-1.930982791781395</v>
       </c>
       <c r="D2" t="n">
         <v>-1.372619831395561</v>
@@ -476,7 +476,7 @@
         <v>-0.4324600236653054</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.1463397933141267</v>
+        <v>-0.1594837480939105</v>
       </c>
       <c r="D3" t="n">
         <v>-0.400889981800908</v>
@@ -492,7 +492,7 @@
         <v>0.3018868326318967</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3767350305831155</v>
+        <v>0.3624418495985551</v>
       </c>
       <c r="D4" t="n">
         <v>0.09509353414700764</v>
@@ -508,7 +508,7 @@
         <v>0.08622628393497969</v>
       </c>
       <c r="C5" t="n">
-        <v>0.07207139829128287</v>
+        <v>0.06951300647730625</v>
       </c>
       <c r="D5" t="n">
         <v>0.08480551191839436</v>
@@ -524,7 +524,7 @@
         <v>0.07941006410819404</v>
       </c>
       <c r="C6" t="n">
-        <v>0.09319649743548022</v>
+        <v>0.09061941657133338</v>
       </c>
       <c r="D6" t="n">
         <v>0.08233754426461207</v>
@@ -540,7 +540,7 @@
         <v>0.09647126130217008</v>
       </c>
       <c r="C7" t="n">
-        <v>0.09554837265743082</v>
+        <v>0.0958539381037443</v>
       </c>
       <c r="D7" t="n">
         <v>0.09309889212543432</v>
@@ -556,7 +556,7 @@
         <v>-0.01878786445224619</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.01432410974989314</v>
+        <v>-0.01844585717249353</v>
       </c>
       <c r="D8" t="n">
         <v>-0.0478992290188085</v>
@@ -572,7 +572,7 @@
         <v>-0.03290485192334106</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.05292743970908468</v>
+        <v>-0.07592609647694451</v>
       </c>
       <c r="D9" t="n">
         <v>-0.1775841739364851</v>
@@ -588,7 +588,7 @@
         <v>0.3483953357708522</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3289679624640249</v>
+        <v>0.3328531442731835</v>
       </c>
       <c r="D10" t="n">
         <v>0.3539353471984567</v>
@@ -604,7 +604,7 @@
         <v>-0.6809113612266906</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.5765869686178934</v>
+        <v>-0.5665592841142248</v>
       </c>
       <c r="D11" t="n">
         <v>-0.445630941533774</v>
@@ -620,7 +620,7 @@
         <v>-0.4373581067872873</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.5158052556150698</v>
+        <v>-0.5149439998913083</v>
       </c>
       <c r="D12" t="n">
         <v>-0.4308008893603412</v>
@@ -636,7 +636,7 @@
         <v>-0.2803581822670167</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.2400501091994265</v>
+        <v>-0.2394219345463922</v>
       </c>
       <c r="D13" t="n">
         <v>-0.220079893467959</v>
@@ -652,7 +652,7 @@
         <v>0.4195235978774553</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4130466624286052</v>
+        <v>0.4130309170922754</v>
       </c>
       <c r="D14" t="n">
         <v>0.4207613757799708</v>
@@ -668,7 +668,7 @@
         <v>0.140302969760727</v>
       </c>
       <c r="C15" t="n">
-        <v>0.06649989208873208</v>
+        <v>0.05248235577723287</v>
       </c>
       <c r="D15" t="n">
         <v>-0.04129235108006517</v>
@@ -684,7 +684,7 @@
         <v>1.4909757814356</v>
       </c>
       <c r="C16" t="n">
-        <v>1.309209272103024</v>
+        <v>1.309110572159341</v>
       </c>
       <c r="D16" t="n">
         <v>1.299047306758968</v>
@@ -700,7 +700,7 @@
         <v>-4.586808972193319</v>
       </c>
       <c r="C17" t="n">
-        <v>-2.903806902757876</v>
+        <v>-2.907059786984741</v>
       </c>
       <c r="D17" t="n">
         <v>-2.945823226328595</v>
@@ -716,7 +716,7 @@
         <v>0.2920734760066747</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3418805874017823</v>
+        <v>0.3324741875784019</v>
       </c>
       <c r="D18" t="n">
         <v>0.1450765671581794</v>
@@ -732,7 +732,7 @@
         <v>2.905157489318497</v>
       </c>
       <c r="C19" t="n">
-        <v>3.349315458954955</v>
+        <v>3.264634412469725</v>
       </c>
       <c r="D19" t="n">
         <v>1.779312994560645</v>
@@ -748,7 +748,7 @@
         <v>-0.1885578641911002</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.241833629459727</v>
+        <v>-0.2313470054078998</v>
       </c>
       <c r="D20" t="n">
         <v>-0.02899557941119176</v>
@@ -764,7 +764,7 @@
         <v>-0.001122750128137846</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0009739479081583249</v>
+        <v>-0.0009487542301950481</v>
       </c>
       <c r="D21" t="n">
         <v>-0.00116655058901435</v>
@@ -780,7 +780,7 @@
         <v>-0.03248373625743606</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.04843287787580079</v>
+        <v>-0.04694976274233228</v>
       </c>
       <c r="D22" t="n">
         <v>-0.04827981137955573</v>
@@ -796,7 +796,7 @@
         <v>-0.01885868423953722</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0188031551219513</v>
+        <v>-0.0188236930936253</v>
       </c>
       <c r="D23" t="n">
         <v>-0.01938721137799903</v>
